--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N32_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N32_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.67810823232291</v>
+        <v>9.535192587752473</v>
       </c>
       <c r="D2" t="n">
-        <v>64.35349128881413</v>
+        <v>10.4574423344323</v>
       </c>
       <c r="E2" t="n">
-        <v>19.8889633926429</v>
+        <v>3.231956551304473</v>
       </c>
       <c r="F2" t="n">
-        <v>20.50506939252168</v>
+        <v>3.332073776284772</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.60217125648998</v>
+        <v>6.760352829179622</v>
       </c>
       <c r="D3" t="n">
-        <v>11.59572429801021</v>
+        <v>1.88430519842666</v>
       </c>
       <c r="E3" t="n">
-        <v>19.8889633926429</v>
+        <v>3.231956551304473</v>
       </c>
       <c r="F3" t="n">
-        <v>20.50506939252168</v>
+        <v>3.332073776284772</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>5.665577237325318</v>
+        <v>0.9206563010653642</v>
       </c>
       <c r="D4" t="n">
-        <v>17.58171037607606</v>
+        <v>2.85702793611236</v>
       </c>
       <c r="E4" t="n">
-        <v>19.8889633926429</v>
+        <v>3.231956551304473</v>
       </c>
       <c r="F4" t="n">
-        <v>20.50506939252168</v>
+        <v>3.332073776284772</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.78096784435319</v>
+        <v>3.701907274707393</v>
       </c>
       <c r="D5" t="n">
-        <v>27.03070778531904</v>
+        <v>4.392490015114345</v>
       </c>
       <c r="E5" t="n">
-        <v>19.8889633926429</v>
+        <v>3.231956551304473</v>
       </c>
       <c r="F5" t="n">
-        <v>20.50506939252168</v>
+        <v>3.332073776284772</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
